--- a/Instrumentos.xlsx
+++ b/Instrumentos.xlsx
@@ -3973,7 +3973,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10"/>
@@ -6019,13 +6019,113 @@
         </is>
       </c>
     </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>PN37D</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>PAE 2028</t>
+        </is>
+      </c>
+      <c r="C114" s="3">
+        <v>47070</v>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>CP41D</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>CGC 2029</t>
+        </is>
+      </c>
+      <c r="C115" s="3">
+        <v>47368</v>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>Vista Energy 2030</t>
+        </is>
+      </c>
+      <c r="C116" s="3">
+        <v>47549</v>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>BF49D</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>BBVA Argentina 2027</t>
+        </is>
+      </c>
+      <c r="C117" s="3">
+        <v>46592</v>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1927"/>
+  <dimension ref="A1:F1937"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10"/>
@@ -45161,6 +45261,226 @@
       </c>
       <c r="F1927" s="1">
         <v>3984.13176</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:6">
+      <c r="A1928" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1928" s="3">
+        <v>45908</v>
+      </c>
+      <c r="C1928" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1928" s="1">
+        <v>3.7808219178</v>
+      </c>
+      <c r="E1928" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1928" s="1">
+        <v>3.7808219178</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:6">
+      <c r="A1929" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1929" s="3">
+        <v>46090</v>
+      </c>
+      <c r="C1929" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1929" s="1">
+        <v>3.7191780822</v>
+      </c>
+      <c r="E1929" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1929" s="1">
+        <v>3.7191780822</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:6">
+      <c r="A1930" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1930" s="3">
+        <v>46272</v>
+      </c>
+      <c r="C1930" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1930" s="1">
+        <v>3.7808219178</v>
+      </c>
+      <c r="E1930" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1930" s="1">
+        <v>3.7808219178</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:6">
+      <c r="A1931" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1931" s="3">
+        <v>46454</v>
+      </c>
+      <c r="C1931" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1931" s="1">
+        <v>3.7191780822</v>
+      </c>
+      <c r="E1931" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1931" s="1">
+        <v>3.7191780822</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:6">
+      <c r="A1932" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1932" s="3">
+        <v>46637</v>
+      </c>
+      <c r="C1932" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1932" s="1">
+        <v>3.7808219178</v>
+      </c>
+      <c r="E1932" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1932" s="1">
+        <v>3.7808219178</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:6">
+      <c r="A1933" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1933" s="3">
+        <v>46819</v>
+      </c>
+      <c r="C1933" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1933" s="1">
+        <v>3.7397260274</v>
+      </c>
+      <c r="E1933" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1933" s="1">
+        <v>3.7397260274</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:6">
+      <c r="A1934" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1934" s="3">
+        <v>47003</v>
+      </c>
+      <c r="C1934" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1934" s="1">
+        <v>3.7808219178</v>
+      </c>
+      <c r="E1934" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1934" s="1">
+        <v>3.7808219178</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:6">
+      <c r="A1935" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1935" s="3">
+        <v>47184</v>
+      </c>
+      <c r="C1935" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1935" s="1">
+        <v>3.7191780822</v>
+      </c>
+      <c r="E1935" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1935" s="1">
+        <v>3.7191780822</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:6">
+      <c r="A1936" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1936" s="3">
+        <v>47368</v>
+      </c>
+      <c r="C1936" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1936" s="1">
+        <v>3.7808219178</v>
+      </c>
+      <c r="E1936" s="1">
+        <v>0</v>
+      </c>
+      <c r="F1936" s="1">
+        <v>3.7808219178</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:6">
+      <c r="A1937" s="1" t="inlineStr">
+        <is>
+          <t>VSCUD</t>
+        </is>
+      </c>
+      <c r="B1937" s="3">
+        <v>47549</v>
+      </c>
+      <c r="C1937" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="D1937" s="1">
+        <v>3.7191780822</v>
+      </c>
+      <c r="E1937" s="1">
+        <v>100</v>
+      </c>
+      <c r="F1937" s="1">
+        <v>103.7191780822</v>
       </c>
     </row>
   </sheetData>
@@ -46716,7 +47036,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C12C03-5D2E-4402-9FEE-10F6AEE7B245}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="19.1640625" customWidth="1"/>
@@ -46927,6 +47247,30 @@
         <v>1492.18</v>
       </c>
       <c r="F11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>D30N6</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="C12" s="3">
+        <v>46280</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46356</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1513.0</v>
+      </c>
+      <c r="F12" s="1">
         <v>0</v>
       </c>
     </row>
